--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h6.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h6.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>1.035</v>
       </c>
       <c r="F2">
-        <v>1.082</v>
+        <v>1.1874</v>
       </c>
       <c r="G2">
-        <v>0.047</v>
+        <v>0.1524</v>
       </c>
       <c r="H2">
-        <v>0.1151</v>
+        <v>0.5764</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>35</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.8407</v>
+        <v>1.1071</v>
       </c>
       <c r="F3">
-        <v>0.905</v>
+        <v>1.0544</v>
       </c>
       <c r="G3">
-        <v>0.06419999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="H3">
-        <v>0.2185</v>
+        <v>-0.0429</v>
       </c>
       <c r="I3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>6</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>2.2004</v>
+        <v>0.9129</v>
       </c>
       <c r="F4">
-        <v>2.1442</v>
+        <v>1.4125</v>
       </c>
       <c r="G4">
-        <v>-0.0563</v>
+        <v>0.4997</v>
       </c>
       <c r="H4">
-        <v>-0.5056</v>
+        <v>1.6245</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N4">
         <v>6</v>
